--- a/DataToAnalyze/open_ended_encoded.xlsx
+++ b/DataToAnalyze/open_ended_encoded.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\localadmin\Documents\GitHub\joan_stelios_avgousti\DataToAnalyze\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steli\Desktop\asidjaiusjd\joan_stelios_avgousti\DataToAnalyze\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CED78BD-6F1F-40D9-8EE8-F0D583241486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA3D9E6-A1C8-435B-AAFA-4AC530B3EB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="206">
   <si>
     <t>ResponseId</t>
   </si>
@@ -475,22 +475,174 @@
     <t xml:space="preserve">stressful experience, aural explanations helped with feeling uneven </t>
   </si>
   <si>
+    <t>R_2Jjg3lGLOE80snf</t>
+  </si>
+  <si>
+    <t>It gave me reassurance that it sees what is happening</t>
+  </si>
+  <si>
+    <t>Neutral because even there were only 2 buttons, they were performing 4 functions which was a little confusing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In version 2, I felt like I had to keep an eye on the road and also 'help' the system. Even though version 1 didn't have buttons, I felt a little more comfortable because I assumed that the car would have been properly tested before hitting the streets. The explanations on version 3 are a nice to have. It gives reassurance without the need for me to press buttons.
+</t>
+  </si>
+  <si>
+    <t>Something I missed was the car indicating the direction it would go to. It's quite important on the road</t>
+  </si>
+  <si>
+    <t>R_2F3avXVwqRbdZWk</t>
+  </si>
+  <si>
+    <t>More trust in the system used for the first time</t>
+  </si>
+  <si>
+    <t>Not so comfortable or intuitive</t>
+  </si>
+  <si>
+    <t>I prefer to know what the vehicle is going to do</t>
+  </si>
+  <si>
+    <t>The lateral control was quite dizzy and makes my trust low</t>
+  </si>
+  <si>
+    <t>R_8aQPykCIrkN1rkQ</t>
+  </si>
+  <si>
+    <t>They made me trust the vehicle more, as I could potentially spot any mistakes, even if it didnt make any. At the same time, if I really trusted the vehicle I would not need any explanations.</t>
+  </si>
+  <si>
+    <t>During the first trial with the control buttons things were pretty confusing. During the second one, where the car's intentions were visible, things made a little more sense.</t>
+  </si>
+  <si>
+    <t>Buttons only create unreliability for responses. The car could be already stopping and you could unknowingly cause a crash like I did. If there is no explanation I would prefer to have to trust the car.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I personally believe that the buttons introduce a weird middle ground between trust and accountability. If the car is really better at driving that humans, then real trust would imply never needing to interfere with the car's actions.  </t>
+  </si>
+  <si>
+    <t>R_2r16cF1wtgTa4l8</t>
+  </si>
+  <si>
+    <t>it gave me more trust.</t>
+  </si>
+  <si>
+    <t>going against my instincts. (both slow down)</t>
+  </si>
+  <si>
+    <t>First version i had to adapt, so i didnt really focus. version 2 felt better then version 3. version 3 had moments when it didnt explain, but i felt like sometimes it drove to close to the curf/car.</t>
+  </si>
+  <si>
+    <t>perhaps a trial zero for people who never did vr before.</t>
+  </si>
+  <si>
+    <t>R_82yV6n7Hwnh8D2e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It made me trust the vehicle less because it didn't always stop or break fast enough for the situation. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The stop/don't stop button did not work properly in the previous simulations, meaning that when i pressed it before it would only stop and never not stop. The one time I needed a hard/quick stop it didn't stop, it just kept going and so I crashed. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Because when you did not have any control over the car, it didn't matter what you felt or did where as when I had explanations and could control the buttons the buttons felt counterintuative from the previous experiences. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The driving experience was relatively nice, a bit slow and not very natural but overall I could trust the car for the basic driving needs. </t>
+  </si>
+  <si>
+    <t>R_240i1i4hXpWXZjr</t>
+  </si>
+  <si>
+    <t>Explaining, added a layer of understanding and made me less wary</t>
+  </si>
+  <si>
+    <t>Easy to manage, after the first trials</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The voice helped ease the transition between stages the car is going through
+</t>
+  </si>
+  <si>
+    <t>Sound would make this more immersive and might change the outcomes but it was still engaging.</t>
+  </si>
+  <si>
+    <t>R_8TGfu6L1KP6Du3V</t>
+  </si>
+  <si>
+    <t>The explanations helped to increase trust given that it allows for me to make the final judgement if I want to accept the decision or not.</t>
+  </si>
+  <si>
+    <t>I think it was good, after understanding that the left one is more like a "go slower for a bit" button it became better.</t>
+  </si>
+  <si>
+    <t>While the car didnt generate distrust allowing me to override the decision made it more comfortable, and also I was more aquainted with the experience by the third trial</t>
+  </si>
+  <si>
+    <t>Very relaxing, although the first one was a bit uncomfortable given that I was still getting aquainted with the experience and had no control over it.</t>
+  </si>
+  <si>
+    <t>R_21idYiYyo38laOJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">make me trust car's reactions </t>
+  </si>
+  <si>
+    <t>I liked it cause it gave me more control</t>
+  </si>
+  <si>
+    <t>I prefer it when I have some level of control</t>
+  </si>
+  <si>
+    <t>it was a fun experience</t>
+  </si>
+  <si>
+    <t>R_2S1ftlbVSMEaaCa</t>
+  </si>
+  <si>
+    <t>Because I knew what the next action of the car was, so it made me more comfortable.</t>
+  </si>
+  <si>
+    <t>The controls were helpful</t>
+  </si>
+  <si>
+    <t>I assigned the version three as the most comfortable one because it was generally more comfortable when I knew what actions to expect from the car, and it felt most comfortable when I was able to control its actions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The experience was fun and interesting. </t>
+  </si>
+  <si>
+    <t>R_8kidpk1vpAV0VcI</t>
+  </si>
+  <si>
+    <t>It influenced my trust since the vehicle did exactly what the explanation said</t>
+  </si>
+  <si>
+    <t>got a bit confused at first but after 1-2 tries i was very comfortable with the buttons</t>
+  </si>
+  <si>
+    <t>version 1 made me feel a bit unsafe not knowing what the actions will be or having no control, version 2 made me feel more comfortable since i had control of the vehicle, version 3, at this point the vehicle gained my full trust since it showed me it is reliable and it also showed me its intentions</t>
+  </si>
+  <si>
+    <t>maybe next time some people can jump in the road out of nowhere so we can see the vehicles reaction</t>
+  </si>
+  <si>
+    <t>positive</t>
+  </si>
+  <si>
+    <t>mixed</t>
+  </si>
+  <si>
+    <t>neutral</t>
+  </si>
+  <si>
+    <t>negative</t>
+  </si>
+  <si>
     <t>btn_theme</t>
   </si>
   <si>
     <t>expl_theme</t>
-  </si>
-  <si>
-    <t>mixed</t>
-  </si>
-  <si>
-    <t>positive</t>
-  </si>
-  <si>
-    <t>neutral</t>
-  </si>
-  <si>
-    <t>negative</t>
   </si>
 </sst>
 </file>
@@ -546,9 +698,7 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -557,10 +707,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -867,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -931,11 +1084,11 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>151</v>
+      <c r="U1" t="s">
+        <v>204</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
@@ -1000,10 +1153,10 @@
         <v>0</v>
       </c>
       <c r="U2" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="V2" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -1068,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="V3" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -1136,10 +1289,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="V4" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -1204,10 +1357,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="V5" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
@@ -1272,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="U6" t="s">
-        <v>154</v>
+        <v>202</v>
       </c>
       <c r="V6" t="s">
-        <v>154</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
@@ -1340,10 +1493,10 @@
         <v>0</v>
       </c>
       <c r="U7" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="V7" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
@@ -1408,10 +1561,10 @@
         <v>0</v>
       </c>
       <c r="U8" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="V8" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
@@ -1476,10 +1629,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="V9" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -1544,10 +1697,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="s">
-        <v>155</v>
+        <v>203</v>
       </c>
       <c r="V10" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -1612,10 +1765,10 @@
         <v>0</v>
       </c>
       <c r="U11" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="V11" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -1680,10 +1833,10 @@
         <v>0</v>
       </c>
       <c r="U12" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="V12" t="s">
-        <v>154</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -1748,10 +1901,10 @@
         <v>0</v>
       </c>
       <c r="U13" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="V13" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -1816,10 +1969,10 @@
         <v>0</v>
       </c>
       <c r="U14" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="V14" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -1884,10 +2037,10 @@
         <v>0</v>
       </c>
       <c r="U15" t="s">
-        <v>154</v>
+        <v>202</v>
       </c>
       <c r="V15" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -1952,10 +2105,10 @@
         <v>0</v>
       </c>
       <c r="U16" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="V16" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
@@ -2020,10 +2173,10 @@
         <v>0</v>
       </c>
       <c r="U17" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="V17" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
@@ -2088,10 +2241,10 @@
         <v>0</v>
       </c>
       <c r="U18" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="V18" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
@@ -2156,10 +2309,10 @@
         <v>0</v>
       </c>
       <c r="U19" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="V19" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
@@ -2224,10 +2377,10 @@
         <v>0</v>
       </c>
       <c r="U20" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="V20" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
@@ -2292,10 +2445,10 @@
         <v>0</v>
       </c>
       <c r="U21" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="V21" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
@@ -2360,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="U22" t="s">
-        <v>155</v>
+        <v>203</v>
       </c>
       <c r="V22" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
@@ -2428,10 +2581,10 @@
         <v>0</v>
       </c>
       <c r="U23" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="V23" t="s">
-        <v>155</v>
+        <v>203</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
@@ -2496,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="U24" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="V24" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
@@ -2564,10 +2717,10 @@
         <v>0</v>
       </c>
       <c r="U25" t="s">
-        <v>154</v>
+        <v>202</v>
       </c>
       <c r="V25" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
@@ -2632,10 +2785,10 @@
         <v>0</v>
       </c>
       <c r="U26" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="V26" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
@@ -2700,10 +2853,690 @@
         <v>0</v>
       </c>
       <c r="U27" t="s">
+        <v>200</v>
+      </c>
+      <c r="V27" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B28">
+        <v>2</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28" t="s">
+        <v>151</v>
+      </c>
+      <c r="F28" t="s">
+        <v>152</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="V27" t="s">
-        <v>153</v>
+      <c r="H28" t="s">
+        <v>154</v>
+      </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" t="b">
+        <v>1</v>
+      </c>
+      <c r="N28" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" t="b">
+        <v>1</v>
+      </c>
+      <c r="P28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="b">
+        <v>1</v>
+      </c>
+      <c r="R28" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="b">
+        <v>0</v>
+      </c>
+      <c r="U28" t="s">
+        <v>203</v>
+      </c>
+      <c r="V28" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29" t="s">
+        <v>156</v>
+      </c>
+      <c r="F29" t="s">
+        <v>157</v>
+      </c>
+      <c r="G29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H29" t="s">
+        <v>159</v>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="b">
+        <v>0</v>
+      </c>
+      <c r="U29" t="s">
+        <v>203</v>
+      </c>
+      <c r="V29" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+      <c r="E30" t="s">
+        <v>161</v>
+      </c>
+      <c r="F30" t="s">
+        <v>162</v>
+      </c>
+      <c r="G30" t="s">
+        <v>163</v>
+      </c>
+      <c r="H30" t="s">
+        <v>164</v>
+      </c>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" t="b">
+        <v>1</v>
+      </c>
+      <c r="N30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" t="s">
+        <v>203</v>
+      </c>
+      <c r="V30" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>165</v>
+      </c>
+      <c r="B31">
+        <v>3</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31" t="s">
+        <v>166</v>
+      </c>
+      <c r="F31" t="s">
+        <v>167</v>
+      </c>
+      <c r="G31" t="s">
+        <v>168</v>
+      </c>
+      <c r="H31" t="s">
+        <v>169</v>
+      </c>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" t="b">
+        <v>0</v>
+      </c>
+      <c r="N31" t="b">
+        <v>0</v>
+      </c>
+      <c r="O31" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="b">
+        <v>0</v>
+      </c>
+      <c r="R31" t="b">
+        <v>0</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="b">
+        <v>0</v>
+      </c>
+      <c r="U31" t="s">
+        <v>202</v>
+      </c>
+      <c r="V31" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
+        <v>171</v>
+      </c>
+      <c r="F32" t="s">
+        <v>172</v>
+      </c>
+      <c r="G32" t="s">
+        <v>173</v>
+      </c>
+      <c r="H32" t="s">
+        <v>174</v>
+      </c>
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="b">
+        <v>1</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="b">
+        <v>0</v>
+      </c>
+      <c r="U32" t="s">
+        <v>203</v>
+      </c>
+      <c r="V32" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>175</v>
+      </c>
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>2</v>
+      </c>
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33" t="s">
+        <v>176</v>
+      </c>
+      <c r="F33" t="s">
+        <v>177</v>
+      </c>
+      <c r="G33" t="s">
+        <v>178</v>
+      </c>
+      <c r="H33" t="s">
+        <v>179</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O33" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>0</v>
+      </c>
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="b">
+        <v>0</v>
+      </c>
+      <c r="U33" t="s">
+        <v>200</v>
+      </c>
+      <c r="V33" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>180</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34" t="s">
+        <v>181</v>
+      </c>
+      <c r="F34" t="s">
+        <v>182</v>
+      </c>
+      <c r="G34" t="s">
+        <v>183</v>
+      </c>
+      <c r="H34" t="s">
+        <v>184</v>
+      </c>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="b">
+        <v>1</v>
+      </c>
+      <c r="L34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O34" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="b">
+        <v>0</v>
+      </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="b">
+        <v>0</v>
+      </c>
+      <c r="U34" t="s">
+        <v>200</v>
+      </c>
+      <c r="V34" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>185</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35">
+        <v>3</v>
+      </c>
+      <c r="E35" t="s">
+        <v>186</v>
+      </c>
+      <c r="F35" t="s">
+        <v>187</v>
+      </c>
+      <c r="G35" t="s">
+        <v>188</v>
+      </c>
+      <c r="H35" t="s">
+        <v>189</v>
+      </c>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35" t="b">
+        <v>0</v>
+      </c>
+      <c r="O35" t="b">
+        <v>0</v>
+      </c>
+      <c r="P35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="b">
+        <v>1</v>
+      </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="b">
+        <v>0</v>
+      </c>
+      <c r="U35" t="s">
+        <v>200</v>
+      </c>
+      <c r="V35" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>190</v>
+      </c>
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="E36" t="s">
+        <v>191</v>
+      </c>
+      <c r="F36" t="s">
+        <v>192</v>
+      </c>
+      <c r="G36" t="s">
+        <v>193</v>
+      </c>
+      <c r="H36" t="s">
+        <v>194</v>
+      </c>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" t="b">
+        <v>0</v>
+      </c>
+      <c r="N36" t="b">
+        <v>0</v>
+      </c>
+      <c r="O36" t="b">
+        <v>0</v>
+      </c>
+      <c r="P36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="b">
+        <v>1</v>
+      </c>
+      <c r="R36" t="b">
+        <v>0</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="b">
+        <v>0</v>
+      </c>
+      <c r="U36" t="s">
+        <v>200</v>
+      </c>
+      <c r="V36" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>195</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37" t="s">
+        <v>196</v>
+      </c>
+      <c r="F37" t="s">
+        <v>197</v>
+      </c>
+      <c r="G37" t="s">
+        <v>198</v>
+      </c>
+      <c r="H37" t="s">
+        <v>199</v>
+      </c>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
+      </c>
+      <c r="O37" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="b">
+        <v>1</v>
+      </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U37" t="s">
+        <v>201</v>
+      </c>
+      <c r="V37" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
